--- a/camp_registration_forms/040_summer_camp_scholarship_application_form--camp_registration_forms.xlsx
+++ b/camp_registration_forms/040_summer_camp_scholarship_application_form--camp_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'income_level_0',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'income_level_0', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'income_level_1',_'label':_'$25,001_-_$35,000'}</t>
+          <t>$25,001_-_$35,000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'income_level_1', 'label': '$25,001 - $35,000'}</t>
+          <t>$25,001 - $35,000</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'income_level_2',_'label':_'$35,001_-_$45,000'}</t>
+          <t>$35,001_-_$45,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'income_level_2', 'label': '$35,001 - $45,000'}</t>
+          <t>$35,001 - $45,000</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'income_level_3',_'label':_'$45,001+'}</t>
+          <t>$45,001+</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'income_level_3', 'label': '$45,001+'}</t>
+          <t>$45,001+</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'income_level_4',_'label':_'undisclosed'}</t>
+          <t>undisclosed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'income_level_4', 'label': 'Undisclosed'}</t>
+          <t>Undisclosed</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'parent_0',_'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'parent_0', 'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'parent_1',_'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'parent_1', 'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'parent_2',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'parent_2', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'parent_3',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'parent_3', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'grade_1',_'label':_'1st_grade'}</t>
+          <t>1st_grade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'grade_1', 'label': '1st Grade'}</t>
+          <t>1st Grade</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'grade_2',_'label':_'2nd_grade'}</t>
+          <t>2nd_grade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'grade_2', 'label': '2nd Grade'}</t>
+          <t>2nd Grade</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'grade_3',_'label':_'3rd_grade'}</t>
+          <t>3rd_grade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'grade_3', 'label': '3rd Grade'}</t>
+          <t>3rd Grade</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'grade_4',_'label':_'4th_grade'}</t>
+          <t>4th_grade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'grade_4', 'label': '4th Grade'}</t>
+          <t>4th Grade</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'grade_5',_'label':_'5th_grade'}</t>
+          <t>5th_grade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'grade_5', 'label': '5th Grade'}</t>
+          <t>5th Grade</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'grade_6',_'label':_'6th_grade'}</t>
+          <t>6th_grade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'grade_6', 'label': '6th Grade'}</t>
+          <t>6th Grade</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'grade_7',_'label':_'7th_grade'}</t>
+          <t>7th_grade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'grade_7', 'label': '7th Grade'}</t>
+          <t>7th Grade</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'grade_8',_'label':_'8th_grade'}</t>
+          <t>8th_grade</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'grade_8', 'label': '8th Grade'}</t>
+          <t>8th Grade</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'grade_9',_'label':_'9th_grade'}</t>
+          <t>9th_grade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'grade_9', 'label': '9th Grade'}</t>
+          <t>9th Grade</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'grade_10',_'label':_'10th_grade'}</t>
+          <t>10th_grade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'grade_10', 'label': '10th Grade'}</t>
+          <t>10th Grade</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
